--- a/Data/FlightPlan/FPL_17SEP26.xlsx
+++ b/Data/FlightPlan/FPL_17SEP26.xlsx
@@ -140,6 +140,69 @@
     <t>DPS</t>
   </si>
   <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>ICN</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
     <t>08:45</t>
   </si>
   <si>
@@ -149,69 +212,6 @@
     <t>17:25</t>
   </si>
   <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>ICN</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
     <t>HYD</t>
   </si>
   <si>
@@ -542,6 +542,9 @@
     <t>VN-A542</t>
   </si>
   <si>
+    <t>09:00</t>
+  </si>
+  <si>
     <t>16:55</t>
   </si>
   <si>
@@ -587,9 +590,6 @@
     <t>06:30</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
     <t>KUL</t>
   </si>
   <si>
@@ -659,6 +659,12 @@
     <t>11:05</t>
   </si>
   <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
     <t>BKK</t>
   </si>
   <si>
@@ -800,9 +806,6 @@
     <t>07:40</t>
   </si>
   <si>
-    <t>09:05</t>
-  </si>
-  <si>
     <t>11:35</t>
   </si>
   <si>
@@ -989,9 +992,6 @@
     <t>11:30</t>
   </si>
   <si>
-    <t>12:00</t>
-  </si>
-  <si>
     <t>01:10</t>
   </si>
   <si>
@@ -1268,7 +1268,7 @@
     <t>Total Record(s): 397</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 16, 2026 22:05</t>
+    <t xml:space="preserve">Generated on  Sep 16, 2026 23:54</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2116,7 +2116,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="7">
-        <v>893</v>
+        <v>849</v>
       </c>
       <c t="s" r="C17" s="7">
         <v>14</v>
@@ -2138,7 +2138,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J17" s="7">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2149,7 +2149,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7">
-        <v>894</v>
+        <v>848</v>
       </c>
       <c t="s" r="C18" s="7">
         <v>14</v>
@@ -2168,10 +2168,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2198,13 +2198,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2228,16 +2228,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G20" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="H20" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2270,22 +2270,22 @@
       </c>
       <c r="D22" s="7"/>
       <c t="s" r="E22" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F22" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G22" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="H22" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I22" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c t="s" r="J22" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -2303,22 +2303,22 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G23" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H23" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
@@ -2345,13 +2345,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H24" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2369,22 +2369,22 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G25" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="H25" s="8">
         <v>53</v>
       </c>
-      <c t="s" r="H25" s="8">
-        <v>52</v>
-      </c>
       <c t="s" r="I25" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2410,14 +2410,14 @@
         <v>13</v>
       </c>
       <c r="B27" s="7">
-        <v>849</v>
+        <v>893</v>
       </c>
       <c t="s" r="C27" s="7">
         <v>14</v>
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
@@ -2429,10 +2429,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2443,14 +2443,14 @@
         <v>13</v>
       </c>
       <c r="B28" s="7">
-        <v>848</v>
+        <v>894</v>
       </c>
       <c t="s" r="C28" s="7">
         <v>14</v>
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -3185,7 +3185,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3404,7 +3404,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>95</v>
@@ -3440,7 +3440,7 @@
         <v>95</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I61" s="7">
         <v>130</v>
@@ -3470,7 +3470,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>95</v>
@@ -3506,7 +3506,7 @@
         <v>95</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="I63" s="7">
         <v>133</v>
@@ -3659,7 +3659,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3689,7 +3689,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>21</v>
@@ -3872,7 +3872,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3977,7 +3977,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>17</v>
@@ -4085,7 +4085,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4456,7 +4456,7 @@
         <v>13</v>
       </c>
       <c r="B95" s="7">
-        <v>973</v>
+        <v>719</v>
       </c>
       <c t="s" r="C95" s="7">
         <v>14</v>
@@ -4472,10 +4472,10 @@
         <v>95</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>158</v>
+        <v>51</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>177</v>
@@ -4489,7 +4489,7 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>814</v>
+        <v>718</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
@@ -4502,16 +4502,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4522,7 +4522,7 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>1156</v>
+        <v>973</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
@@ -4535,16 +4535,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4555,7 +4555,7 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>169</v>
+        <v>814</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
@@ -4568,32 +4568,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
+      <c t="s" r="A99" s="6">
+        <v>13</v>
+      </c>
+      <c r="B99" s="7">
+        <v>1156</v>
+      </c>
+      <c t="s" r="C99" s="7">
+        <v>14</v>
+      </c>
       <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="7"/>
+      <c t="s" r="E99" s="7">
+        <v>176</v>
+      </c>
+      <c r="F99" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G99" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H99" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I99" s="7">
+        <v>97</v>
+      </c>
+      <c t="s" r="J99" s="7">
+        <v>161</v>
+      </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
@@ -4603,63 +4621,45 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>969</v>
+        <v>169</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
+        <v>176</v>
+      </c>
+      <c r="F100" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G100" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H100" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I100" s="7">
+        <v>82</v>
+      </c>
+      <c t="s" r="J100" s="7">
         <v>180</v>
-      </c>
-      <c r="F100" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G100" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H100" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="I100" s="7">
-        <v>181</v>
-      </c>
-      <c t="s" r="J100" s="7">
-        <v>182</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c t="s" r="A101" s="6">
-        <v>13</v>
-      </c>
-      <c r="B101" s="7">
-        <v>986</v>
-      </c>
-      <c t="s" r="C101" s="7">
-        <v>14</v>
-      </c>
+      <c r="A101" s="6"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
       <c r="D101" s="7"/>
-      <c t="s" r="E101" s="7">
-        <v>180</v>
-      </c>
-      <c r="F101" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G101" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="H101" s="8">
-        <v>183</v>
-      </c>
-      <c t="s" r="I101" s="7">
-        <v>184</v>
-      </c>
-      <c t="s" r="J101" s="7">
-        <v>185</v>
-      </c>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
@@ -4669,29 +4669,29 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c t="s" r="C102" s="7">
         <v>14</v>
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H102" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="I102" s="7">
+        <v>182</v>
+      </c>
+      <c t="s" r="J102" s="7">
         <v>183</v>
-      </c>
-      <c t="s" r="H102" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="I102" s="7">
-        <v>186</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>187</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4702,45 +4702,63 @@
         <v>13</v>
       </c>
       <c r="B103" s="7">
-        <v>322</v>
+        <v>986</v>
       </c>
       <c t="s" r="C103" s="7">
         <v>14</v>
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>41</v>
+        <v>184</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
+      <c t="s" r="A104" s="6">
+        <v>13</v>
+      </c>
+      <c r="B104" s="7">
+        <v>985</v>
+      </c>
+      <c t="s" r="C104" s="7">
+        <v>14</v>
+      </c>
       <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="7"/>
+      <c t="s" r="E104" s="7">
+        <v>181</v>
+      </c>
+      <c r="F104" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G104" s="8">
+        <v>184</v>
+      </c>
+      <c t="s" r="H104" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="I104" s="7">
+        <v>187</v>
+      </c>
+      <c t="s" r="J104" s="7">
+        <v>188</v>
+      </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
@@ -4750,63 +4768,45 @@
         <v>13</v>
       </c>
       <c r="B105" s="7">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c t="s" r="C105" s="7">
         <v>14</v>
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
+        <v>181</v>
+      </c>
+      <c r="F105" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G105" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="H105" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I105" s="7">
+        <v>81</v>
+      </c>
+      <c t="s" r="J105" s="7">
         <v>189</v>
-      </c>
-      <c r="F105" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G105" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H105" s="8">
-        <v>190</v>
-      </c>
-      <c t="s" r="I105" s="7">
-        <v>191</v>
-      </c>
-      <c t="s" r="J105" s="7">
-        <v>137</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c t="s" r="A106" s="6">
-        <v>13</v>
-      </c>
-      <c r="B106" s="7">
-        <v>351</v>
-      </c>
-      <c t="s" r="C106" s="7">
-        <v>14</v>
-      </c>
+      <c r="A106" s="6"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
       <c r="D106" s="7"/>
-      <c t="s" r="E106" s="7">
-        <v>189</v>
-      </c>
-      <c r="F106" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G106" s="8">
-        <v>190</v>
-      </c>
-      <c t="s" r="H106" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I106" s="7">
-        <v>39</v>
-      </c>
-      <c t="s" r="J106" s="7">
-        <v>192</v>
-      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
@@ -4816,14 +4816,14 @@
         <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>1813</v>
+        <v>350</v>
       </c>
       <c t="s" r="C107" s="7">
         <v>14</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4832,13 +4832,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4849,29 +4849,29 @@
         <v>13</v>
       </c>
       <c r="B108" s="7">
-        <v>1814</v>
+        <v>351</v>
       </c>
       <c t="s" r="C108" s="7">
         <v>14</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4882,14 +4882,14 @@
         <v>13</v>
       </c>
       <c r="B109" s="7">
-        <v>150</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C109" s="7">
         <v>14</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4898,29 +4898,47 @@
         <v>41</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
+      <c t="s" r="A110" s="6">
+        <v>13</v>
+      </c>
+      <c r="B110" s="7">
+        <v>1814</v>
+      </c>
+      <c t="s" r="C110" s="7">
+        <v>14</v>
+      </c>
       <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
+      <c t="s" r="E110" s="7">
+        <v>190</v>
+      </c>
+      <c r="F110" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G110" s="8">
+        <v>193</v>
+      </c>
+      <c t="s" r="H110" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I110" s="7">
+        <v>59</v>
+      </c>
+      <c t="s" r="J110" s="7">
+        <v>168</v>
+      </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
@@ -4930,14 +4948,14 @@
         <v>13</v>
       </c>
       <c r="B111" s="7">
-        <v>3788</v>
+        <v>150</v>
       </c>
       <c t="s" r="C111" s="7">
         <v>14</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4946,47 +4964,29 @@
         <v>41</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>197</v>
+        <v>30</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c t="s" r="A112" s="6">
-        <v>13</v>
-      </c>
-      <c r="B112" s="7">
-        <v>3789</v>
-      </c>
-      <c t="s" r="C112" s="7">
-        <v>14</v>
-      </c>
+      <c r="A112" s="6"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
       <c r="D112" s="7"/>
-      <c t="s" r="E112" s="7">
-        <v>196</v>
-      </c>
-      <c r="F112" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G112" s="8">
-        <v>197</v>
-      </c>
-      <c t="s" r="H112" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I112" s="7">
-        <v>200</v>
-      </c>
-      <c t="s" r="J112" s="7">
-        <v>201</v>
-      </c>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
@@ -4996,7 +4996,7 @@
         <v>13</v>
       </c>
       <c r="B113" s="7">
-        <v>3908</v>
+        <v>3788</v>
       </c>
       <c t="s" r="C113" s="7">
         <v>14</v>
@@ -5012,13 +5012,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5026,10 +5026,10 @@
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B114" s="7">
-        <v>3909</v>
+        <v>3789</v>
       </c>
       <c t="s" r="C114" s="7">
         <v>14</v>
@@ -5042,98 +5042,98 @@
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
+      <c t="s" r="A115" s="6">
+        <v>13</v>
+      </c>
+      <c r="B115" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C115" s="7">
+        <v>14</v>
+      </c>
       <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="7"/>
+      <c t="s" r="E115" s="7">
+        <v>196</v>
+      </c>
+      <c r="F115" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G115" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H115" s="8">
+        <v>202</v>
+      </c>
+      <c t="s" r="I115" s="7">
+        <v>203</v>
+      </c>
+      <c t="s" r="J115" s="7">
+        <v>204</v>
+      </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c r="M115" s="7"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c t="s" r="A116" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B116" s="7">
-        <v>930</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C116" s="7">
         <v>14</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>30</v>
+        <v>202</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c r="M116" s="7"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c t="s" r="A117" s="6">
-        <v>13</v>
-      </c>
-      <c r="B117" s="7">
-        <v>931</v>
-      </c>
-      <c t="s" r="C117" s="7">
-        <v>14</v>
-      </c>
+      <c r="A117" s="6"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
       <c r="D117" s="7"/>
-      <c t="s" r="E117" s="7">
-        <v>207</v>
-      </c>
-      <c r="F117" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G117" s="8">
-        <v>208</v>
-      </c>
-      <c t="s" r="H117" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I117" s="7">
-        <v>209</v>
-      </c>
-      <c t="s" r="J117" s="7">
-        <v>210</v>
-      </c>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
@@ -5143,7 +5143,7 @@
         <v>13</v>
       </c>
       <c r="B118" s="7">
-        <v>519</v>
+        <v>930</v>
       </c>
       <c t="s" r="C118" s="7">
         <v>14</v>
@@ -5159,13 +5159,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>211</v>
+        <v>43</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>212</v>
+        <v>59</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5176,7 +5176,7 @@
         <v>13</v>
       </c>
       <c r="B119" s="7">
-        <v>522</v>
+        <v>931</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
@@ -5189,32 +5189,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
+      <c t="s" r="A120" s="6">
+        <v>13</v>
+      </c>
+      <c r="B120" s="7">
+        <v>519</v>
+      </c>
+      <c t="s" r="C120" s="7">
+        <v>14</v>
+      </c>
       <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
+      <c t="s" r="E120" s="7">
+        <v>207</v>
+      </c>
+      <c r="F120" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G120" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H120" s="8">
+        <v>95</v>
+      </c>
+      <c t="s" r="I120" s="7">
+        <v>211</v>
+      </c>
+      <c t="s" r="J120" s="7">
+        <v>212</v>
+      </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c r="M120" s="7"/>
@@ -5224,63 +5242,45 @@
         <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>869</v>
+        <v>522</v>
       </c>
       <c t="s" r="C121" s="7">
         <v>14</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>214</v>
+        <v>150</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c t="s" r="A122" s="6">
-        <v>13</v>
-      </c>
-      <c r="B122" s="7">
-        <v>807</v>
-      </c>
-      <c t="s" r="C122" s="7">
-        <v>14</v>
-      </c>
+      <c r="A122" s="6"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
       <c r="D122" s="7"/>
-      <c t="s" r="E122" s="7">
-        <v>213</v>
-      </c>
-      <c r="F122" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G122" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H122" s="8">
-        <v>216</v>
-      </c>
-      <c t="s" r="I122" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="J122" s="7">
-        <v>217</v>
-      </c>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
@@ -5290,7 +5290,7 @@
         <v>13</v>
       </c>
       <c r="B123" s="7">
-        <v>800</v>
+        <v>869</v>
       </c>
       <c t="s" r="C123" s="7">
         <v>14</v>
@@ -5303,27 +5303,31 @@
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H123" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I123" s="7">
+        <v>214</v>
+      </c>
+      <c t="s" r="J123" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="K123" s="7">
         <v>216</v>
       </c>
-      <c t="s" r="H123" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I123" s="7">
-        <v>218</v>
-      </c>
-      <c t="s" r="J123" s="7">
-        <v>219</v>
-      </c>
-      <c r="K123" s="7"/>
       <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
+      <c t="s" r="M123" s="7">
+        <v>217</v>
+      </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
         <v>13</v>
       </c>
       <c r="B124" s="7">
-        <v>3900</v>
+        <v>807</v>
       </c>
       <c t="s" r="C124" s="7">
         <v>14</v>
@@ -5339,13 +5343,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5353,10 +5357,10 @@
     </row>
     <row r="125" ht="15" customHeight="1">
       <c t="s" r="A125" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B125" s="7">
-        <v>3901</v>
+        <v>800</v>
       </c>
       <c t="s" r="C125" s="7">
         <v>14</v>
@@ -5369,7 +5373,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>41</v>
@@ -5385,82 +5389,82 @@
       <c r="M125" s="7"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="6"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
+      <c t="s" r="A126" s="6">
+        <v>13</v>
+      </c>
+      <c r="B126" s="7">
+        <v>3900</v>
+      </c>
+      <c t="s" r="C126" s="7">
+        <v>14</v>
+      </c>
       <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="8"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
+      <c t="s" r="E126" s="7">
+        <v>213</v>
+      </c>
+      <c r="F126" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G126" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H126" s="8">
+        <v>149</v>
+      </c>
+      <c t="s" r="I126" s="7">
+        <v>81</v>
+      </c>
+      <c t="s" r="J126" s="7">
+        <v>108</v>
+      </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c r="M126" s="7"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c t="s" r="A127" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B127" s="7">
-        <v>447</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C127" s="7">
         <v>14</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
+        <v>213</v>
+      </c>
+      <c r="F127" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G127" s="8">
+        <v>149</v>
+      </c>
+      <c t="s" r="H127" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I127" s="7">
         <v>222</v>
       </c>
-      <c r="F127" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G127" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H127" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="I127" s="7">
-        <v>43</v>
-      </c>
       <c t="s" r="J127" s="7">
-        <v>156</v>
+        <v>223</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c t="s" r="A128" s="6">
-        <v>13</v>
-      </c>
-      <c r="B128" s="7">
-        <v>440</v>
-      </c>
-      <c t="s" r="C128" s="7">
-        <v>14</v>
-      </c>
+      <c r="A128" s="6"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
       <c r="D128" s="7"/>
-      <c t="s" r="E128" s="7">
-        <v>222</v>
-      </c>
-      <c r="F128" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G128" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="H128" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I128" s="7">
-        <v>223</v>
-      </c>
-      <c t="s" r="J128" s="7">
-        <v>114</v>
-      </c>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="7"/>
+      <c r="J128" s="7"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c r="M128" s="7"/>
@@ -5470,14 +5474,14 @@
         <v>13</v>
       </c>
       <c r="B129" s="7">
-        <v>511</v>
+        <v>447</v>
       </c>
       <c t="s" r="C129" s="7">
         <v>14</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5486,29 +5490,47 @@
         <v>30</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
+      <c t="s" r="A130" s="6">
+        <v>13</v>
+      </c>
+      <c r="B130" s="7">
+        <v>440</v>
+      </c>
+      <c t="s" r="C130" s="7">
+        <v>14</v>
+      </c>
       <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
+      <c t="s" r="E130" s="7">
+        <v>224</v>
+      </c>
+      <c r="F130" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G130" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="H130" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I130" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J130" s="7">
+        <v>114</v>
+      </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
@@ -5518,63 +5540,45 @@
         <v>13</v>
       </c>
       <c r="B131" s="7">
-        <v>7705</v>
+        <v>511</v>
       </c>
       <c t="s" r="C131" s="7">
         <v>14</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H131" s="8">
+        <v>95</v>
+      </c>
+      <c t="s" r="I131" s="7">
         <v>226</v>
       </c>
-      <c t="s" r="H131" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I131" s="7">
-        <v>129</v>
-      </c>
       <c t="s" r="J131" s="7">
-        <v>184</v>
+        <v>93</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c t="s" r="A132" s="6">
-        <v>13</v>
-      </c>
-      <c r="B132" s="7">
-        <v>7705</v>
-      </c>
-      <c t="s" r="C132" s="7">
-        <v>14</v>
-      </c>
+      <c r="A132" s="6"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
       <c r="D132" s="7"/>
-      <c t="s" r="E132" s="7">
-        <v>225</v>
-      </c>
-      <c r="F132" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G132" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H132" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I132" s="7">
-        <v>75</v>
-      </c>
-      <c t="s" r="J132" s="7">
-        <v>44</v>
-      </c>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="7"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
@@ -5584,29 +5588,29 @@
         <v>13</v>
       </c>
       <c r="B133" s="7">
-        <v>7614</v>
+        <v>7705</v>
       </c>
       <c t="s" r="C133" s="7">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5614,17 +5618,17 @@
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c t="s" r="A134" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B134" s="7">
-        <v>7614</v>
+        <v>7705</v>
       </c>
       <c t="s" r="C134" s="7">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5633,46 +5637,64 @@
         <v>30</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>228</v>
+        <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>229</v>
+        <v>65</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
+      <c t="s" r="A135" s="6">
+        <v>13</v>
+      </c>
+      <c r="B135" s="7">
+        <v>7614</v>
+      </c>
+      <c t="s" r="C135" s="7">
+        <v>118</v>
+      </c>
       <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
+      <c t="s" r="E135" s="7">
+        <v>227</v>
+      </c>
+      <c r="F135" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G135" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H135" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I135" s="7">
+        <v>161</v>
+      </c>
+      <c t="s" r="J135" s="7">
+        <v>229</v>
+      </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c t="s" r="A136" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B136" s="7">
-        <v>929</v>
+        <v>7614</v>
       </c>
       <c t="s" r="C136" s="7">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5681,10 +5703,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>111</v>
+        <v>230</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>231</v>
@@ -5694,34 +5716,16 @@
       <c r="M136" s="7"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c t="s" r="A137" s="6">
-        <v>13</v>
-      </c>
-      <c r="B137" s="7">
-        <v>928</v>
-      </c>
-      <c t="s" r="C137" s="7">
-        <v>14</v>
-      </c>
+      <c r="A137" s="6"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
       <c r="D137" s="7"/>
-      <c t="s" r="E137" s="7">
-        <v>230</v>
-      </c>
-      <c r="F137" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G137" s="8">
-        <v>111</v>
-      </c>
-      <c t="s" r="H137" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I137" s="7">
-        <v>65</v>
-      </c>
-      <c t="s" r="J137" s="7">
-        <v>132</v>
-      </c>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="7"/>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
@@ -5731,14 +5735,14 @@
         <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>971</v>
+        <v>929</v>
       </c>
       <c t="s" r="C138" s="7">
         <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5747,13 +5751,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5761,114 +5765,114 @@
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c t="s" r="A139" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B139" s="7">
-        <v>972</v>
+        <v>928</v>
       </c>
       <c t="s" r="C139" s="7">
         <v>14</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
     </row>
     <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="6"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
+      <c t="s" r="A140" s="6">
+        <v>13</v>
+      </c>
+      <c r="B140" s="7">
+        <v>971</v>
+      </c>
+      <c t="s" r="C140" s="7">
+        <v>14</v>
+      </c>
       <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="8"/>
-      <c r="H140" s="8"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
+      <c t="s" r="E140" s="7">
+        <v>232</v>
+      </c>
+      <c r="F140" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G140" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H140" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="I140" s="7">
+        <v>48</v>
+      </c>
+      <c t="s" r="J140" s="7">
+        <v>161</v>
+      </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c t="s" r="A141" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B141" s="7">
-        <v>829</v>
+        <v>972</v>
       </c>
       <c t="s" r="C141" s="7">
         <v>14</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
+        <v>232</v>
+      </c>
+      <c r="F141" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G141" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="H141" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I141" s="7">
         <v>235</v>
       </c>
-      <c r="F141" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G141" s="8">
-        <v>208</v>
-      </c>
-      <c t="s" r="H141" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I141" s="7">
-        <v>31</v>
-      </c>
       <c t="s" r="J141" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c t="s" r="A142" s="6">
-        <v>13</v>
-      </c>
-      <c r="B142" s="7">
-        <v>362</v>
-      </c>
-      <c t="s" r="C142" s="7">
-        <v>14</v>
-      </c>
+      <c r="A142" s="6"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
       <c r="D142" s="7"/>
-      <c t="s" r="E142" s="7">
-        <v>235</v>
-      </c>
-      <c r="F142" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G142" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H142" s="8">
-        <v>157</v>
-      </c>
-      <c t="s" r="I142" s="7">
-        <v>44</v>
-      </c>
-      <c t="s" r="J142" s="7">
-        <v>209</v>
-      </c>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
@@ -5878,29 +5882,29 @@
         <v>13</v>
       </c>
       <c r="B143" s="7">
-        <v>363</v>
+        <v>829</v>
       </c>
       <c t="s" r="C143" s="7">
         <v>14</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>199</v>
+        <v>31</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5911,14 +5915,14 @@
         <v>13</v>
       </c>
       <c r="B144" s="7">
-        <v>248</v>
+        <v>362</v>
       </c>
       <c t="s" r="C144" s="7">
         <v>14</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5927,13 +5931,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5944,29 +5948,29 @@
         <v>13</v>
       </c>
       <c r="B145" s="7">
-        <v>249</v>
+        <v>363</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5974,17 +5978,17 @@
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c t="s" r="A146" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>828</v>
+        <v>248</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5993,39 +5997,57 @@
         <v>41</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>236</v>
+        <v>142</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
+      <c t="s" r="A147" s="6">
+        <v>13</v>
+      </c>
+      <c r="B147" s="7">
+        <v>249</v>
+      </c>
+      <c t="s" r="C147" s="7">
+        <v>14</v>
+      </c>
       <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="8"/>
-      <c r="H147" s="8"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
+      <c t="s" r="E147" s="7">
+        <v>237</v>
+      </c>
+      <c r="F147" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G147" s="8">
+        <v>86</v>
+      </c>
+      <c t="s" r="H147" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I147" s="7">
+        <v>212</v>
+      </c>
+      <c t="s" r="J147" s="7">
+        <v>144</v>
+      </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c r="M147" s="7"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c t="s" r="A148" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B148" s="7">
-        <v>124</v>
+        <v>828</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
@@ -6041,47 +6063,29 @@
         <v>41</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>30</v>
+        <v>208</v>
       </c>
       <c t="s" r="I148" s="7">
+        <v>108</v>
+      </c>
+      <c t="s" r="J148" s="7">
         <v>238</v>
-      </c>
-      <c t="s" r="J148" s="7">
-        <v>239</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c r="M148" s="7"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c t="s" r="A149" s="6">
-        <v>13</v>
-      </c>
-      <c r="B149" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="C149" s="7">
-        <v>14</v>
-      </c>
+      <c r="A149" s="6"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
       <c r="D149" s="7"/>
-      <c t="s" r="E149" s="7">
-        <v>237</v>
-      </c>
-      <c r="F149" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G149" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H149" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I149" s="7">
-        <v>43</v>
-      </c>
-      <c t="s" r="J149" s="7">
-        <v>18</v>
-      </c>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="7"/>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
@@ -6091,14 +6095,14 @@
         <v>13</v>
       </c>
       <c r="B150" s="7">
-        <v>860</v>
+        <v>124</v>
       </c>
       <c t="s" r="C150" s="7">
         <v>14</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6107,13 +6111,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6124,45 +6128,63 @@
         <v>13</v>
       </c>
       <c r="B151" s="7">
-        <v>861</v>
+        <v>129</v>
       </c>
       <c t="s" r="C151" s="7">
         <v>14</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="7"/>
+      <c t="s" r="A152" s="6">
+        <v>13</v>
+      </c>
+      <c r="B152" s="7">
+        <v>860</v>
+      </c>
+      <c t="s" r="C152" s="7">
+        <v>14</v>
+      </c>
       <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="8"/>
-      <c r="H152" s="8"/>
-      <c r="I152" s="7"/>
-      <c r="J152" s="7"/>
+      <c t="s" r="E152" s="7">
+        <v>239</v>
+      </c>
+      <c r="F152" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G152" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H152" s="8">
+        <v>53</v>
+      </c>
+      <c t="s" r="I152" s="7">
+        <v>185</v>
+      </c>
+      <c t="s" r="J152" s="7">
+        <v>211</v>
+      </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
@@ -6172,78 +6194,78 @@
         <v>13</v>
       </c>
       <c r="B153" s="7">
-        <v>7621</v>
+        <v>861</v>
       </c>
       <c t="s" r="C153" s="7">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c r="M153" s="7"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c t="s" r="A154" s="6">
-        <v>13</v>
-      </c>
-      <c r="B154" s="7">
-        <v>776</v>
-      </c>
-      <c t="s" r="C154" s="7">
-        <v>14</v>
-      </c>
+      <c r="A154" s="6"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
       <c r="D154" s="7"/>
-      <c t="s" r="E154" s="7">
-        <v>240</v>
-      </c>
-      <c r="F154" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G154" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H154" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I154" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="J154" s="7">
-        <v>241</v>
-      </c>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="8"/>
+      <c r="H154" s="8"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="7"/>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c r="M154" s="7"/>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
+      <c t="s" r="A155" s="6">
+        <v>13</v>
+      </c>
+      <c r="B155" s="7">
+        <v>7621</v>
+      </c>
+      <c t="s" r="C155" s="7">
+        <v>118</v>
+      </c>
       <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="8"/>
-      <c r="H155" s="8"/>
-      <c r="I155" s="7"/>
-      <c r="J155" s="7"/>
+      <c t="s" r="E155" s="7">
+        <v>242</v>
+      </c>
+      <c r="F155" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G155" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H155" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I155" s="7">
+        <v>177</v>
+      </c>
+      <c t="s" r="J155" s="7">
+        <v>139</v>
+      </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c r="M155" s="7"/>
@@ -6253,7 +6275,7 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>809</v>
+        <v>776</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
@@ -6266,50 +6288,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="H156" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I156" s="7">
+        <v>36</v>
+      </c>
+      <c t="s" r="J156" s="7">
         <v>243</v>
-      </c>
-      <c t="s" r="I156" s="7">
-        <v>88</v>
-      </c>
-      <c t="s" r="J156" s="7">
-        <v>18</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c r="M156" s="7"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c t="s" r="A157" s="6">
-        <v>13</v>
-      </c>
-      <c r="B157" s="7">
-        <v>808</v>
-      </c>
-      <c t="s" r="C157" s="7">
-        <v>14</v>
-      </c>
+      <c r="A157" s="6"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
       <c r="D157" s="7"/>
-      <c t="s" r="E157" s="7">
-        <v>242</v>
-      </c>
-      <c r="F157" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G157" s="8">
-        <v>243</v>
-      </c>
-      <c t="s" r="H157" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I157" s="7">
-        <v>244</v>
-      </c>
-      <c t="s" r="J157" s="7">
-        <v>245</v>
-      </c>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
@@ -6319,14 +6323,14 @@
         <v>13</v>
       </c>
       <c r="B158" s="7">
-        <v>876</v>
+        <v>809</v>
       </c>
       <c t="s" r="C158" s="7">
         <v>14</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6335,13 +6339,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>246</v>
+        <v>88</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>187</v>
+        <v>18</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6352,29 +6356,29 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>877</v>
+        <v>808</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>23</v>
+        <v>247</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6382,17 +6386,17 @@
     </row>
     <row r="160" ht="15" customHeight="1">
       <c t="s" r="A160" s="6">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6401,46 +6405,64 @@
         <v>41</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="6"/>
-      <c r="B161" s="7"/>
-      <c r="C161" s="7"/>
+      <c t="s" r="A161" s="6">
+        <v>13</v>
+      </c>
+      <c r="B161" s="7">
+        <v>877</v>
+      </c>
+      <c t="s" r="C161" s="7">
+        <v>14</v>
+      </c>
       <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
-      <c r="G161" s="8"/>
-      <c r="H161" s="8"/>
-      <c r="I161" s="7"/>
-      <c r="J161" s="7"/>
+      <c t="s" r="E161" s="7">
+        <v>244</v>
+      </c>
+      <c r="F161" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G161" s="8">
+        <v>184</v>
+      </c>
+      <c t="s" r="H161" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I161" s="7">
+        <v>201</v>
+      </c>
+      <c t="s" r="J161" s="7">
+        <v>23</v>
+      </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c t="s" r="A162" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B162" s="7">
-        <v>1630</v>
+        <v>862</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6449,47 +6471,29 @@
         <v>41</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>249</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>250</v>
+        <v>129</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c t="s" r="A163" s="6">
-        <v>13</v>
-      </c>
-      <c r="B163" s="7">
-        <v>1643</v>
-      </c>
-      <c t="s" r="C163" s="7">
-        <v>14</v>
-      </c>
+      <c r="A163" s="6"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
       <c r="D163" s="7"/>
-      <c t="s" r="E163" s="7">
-        <v>248</v>
-      </c>
-      <c r="F163" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G163" s="8">
-        <v>95</v>
-      </c>
-      <c t="s" r="H163" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I163" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J163" s="7">
-        <v>214</v>
-      </c>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="8"/>
+      <c r="H163" s="8"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="7"/>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
@@ -6499,14 +6503,14 @@
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>630</v>
+        <v>1630</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>14</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6518,10 +6522,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6532,14 +6536,14 @@
         <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>629</v>
+        <v>1643</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6551,10 +6555,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6565,14 +6569,14 @@
         <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c t="s" r="C166" s="7">
         <v>14</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6584,7 +6588,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>253</v>
@@ -6598,14 +6602,14 @@
         <v>13</v>
       </c>
       <c r="B167" s="7">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6617,26 +6621,44 @@
         <v>41</v>
       </c>
       <c t="s" r="I167" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="J167" s="7">
         <v>254</v>
-      </c>
-      <c t="s" r="J167" s="7">
-        <v>48</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="6"/>
-      <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
+      <c t="s" r="A168" s="6">
+        <v>13</v>
+      </c>
+      <c r="B168" s="7">
+        <v>636</v>
+      </c>
+      <c t="s" r="C168" s="7">
+        <v>14</v>
+      </c>
       <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-      <c r="G168" s="8"/>
-      <c r="H168" s="8"/>
-      <c r="I168" s="7"/>
-      <c r="J168" s="7"/>
+      <c t="s" r="E168" s="7">
+        <v>250</v>
+      </c>
+      <c r="F168" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G168" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H168" s="8">
+        <v>95</v>
+      </c>
+      <c t="s" r="I168" s="7">
+        <v>233</v>
+      </c>
+      <c t="s" r="J168" s="7">
+        <v>255</v>
+      </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
@@ -6646,63 +6668,45 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>421</v>
+        <v>647</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c t="s" r="H169" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I169" s="7">
         <v>256</v>
       </c>
-      <c t="s" r="I169" s="7">
-        <v>257</v>
-      </c>
       <c t="s" r="J169" s="7">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
     <row r="170" ht="15" customHeight="1">
-      <c t="s" r="A170" s="6">
-        <v>13</v>
-      </c>
-      <c r="B170" s="7">
-        <v>422</v>
-      </c>
-      <c t="s" r="C170" s="7">
-        <v>14</v>
-      </c>
+      <c r="A170" s="6"/>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
       <c r="D170" s="7"/>
-      <c t="s" r="E170" s="7">
-        <v>255</v>
-      </c>
-      <c r="F170" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G170" s="8">
-        <v>256</v>
-      </c>
-      <c t="s" r="H170" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I170" s="7">
-        <v>258</v>
-      </c>
-      <c t="s" r="J170" s="7">
-        <v>156</v>
-      </c>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="8"/>
+      <c r="H170" s="8"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="7"/>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
@@ -6712,14 +6716,14 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6728,13 +6732,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>53</v>
+        <v>258</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>259</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6745,29 +6749,29 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>53</v>
+        <v>258</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6778,14 +6782,14 @@
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>781</v>
+        <v>451</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6794,13 +6798,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>132</v>
+        <v>261</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>260</v>
+        <v>92</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6811,45 +6815,63 @@
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>834</v>
+        <v>454</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c r="M174" s="7"/>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
+      <c t="s" r="A175" s="6">
+        <v>13</v>
+      </c>
+      <c r="B175" s="7">
+        <v>781</v>
+      </c>
+      <c t="s" r="C175" s="7">
+        <v>14</v>
+      </c>
       <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="8"/>
-      <c r="H175" s="8"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="7"/>
+      <c t="s" r="E175" s="7">
+        <v>257</v>
+      </c>
+      <c r="F175" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G175" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H175" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I175" s="7">
+        <v>132</v>
+      </c>
+      <c t="s" r="J175" s="7">
+        <v>262</v>
+      </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c r="M175" s="7"/>
@@ -6859,63 +6881,45 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>123</v>
+        <v>834</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>262</v>
+        <v>71</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c r="M176" s="7"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c t="s" r="A177" s="6">
-        <v>13</v>
-      </c>
-      <c r="B177" s="7">
-        <v>272</v>
-      </c>
-      <c t="s" r="C177" s="7">
-        <v>14</v>
-      </c>
+      <c r="A177" s="6"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
       <c r="D177" s="7"/>
-      <c t="s" r="E177" s="7">
-        <v>261</v>
-      </c>
-      <c r="F177" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G177" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H177" s="8">
-        <v>91</v>
-      </c>
-      <c t="s" r="I177" s="7">
-        <v>263</v>
-      </c>
-      <c t="s" r="J177" s="7">
-        <v>215</v>
-      </c>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="8"/>
+      <c r="H177" s="8"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="7"/>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c r="M177" s="7"/>
@@ -6925,29 +6929,29 @@
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>273</v>
+        <v>123</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I178" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="J178" s="7">
         <v>264</v>
-      </c>
-      <c t="s" r="J178" s="7">
-        <v>19</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6958,14 +6962,14 @@
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>140</v>
+        <v>272</v>
       </c>
       <c t="s" r="C179" s="7">
         <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6974,13 +6978,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6991,29 +6995,29 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>465</v>
+        <v>273</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>266</v>
+        <v>41</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>267</v>
+        <v>19</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7024,45 +7028,63 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>466</v>
+        <v>140</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>266</v>
+        <v>41</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" s="6"/>
-      <c r="B182" s="7"/>
-      <c r="C182" s="7"/>
+      <c t="s" r="A182" s="6">
+        <v>13</v>
+      </c>
+      <c r="B182" s="7">
+        <v>465</v>
+      </c>
+      <c t="s" r="C182" s="7">
+        <v>14</v>
+      </c>
       <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
-      <c r="G182" s="8"/>
-      <c r="H182" s="8"/>
-      <c r="I182" s="7"/>
-      <c r="J182" s="7"/>
+      <c t="s" r="E182" s="7">
+        <v>263</v>
+      </c>
+      <c r="F182" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G182" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H182" s="8">
+        <v>267</v>
+      </c>
+      <c t="s" r="I182" s="7">
+        <v>200</v>
+      </c>
+      <c t="s" r="J182" s="7">
+        <v>268</v>
+      </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
@@ -7072,63 +7094,45 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>126</v>
+        <v>466</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>41</v>
+        <v>267</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c t="s" r="A184" s="6">
-        <v>13</v>
-      </c>
-      <c r="B184" s="7">
-        <v>131</v>
-      </c>
-      <c t="s" r="C184" s="7">
-        <v>14</v>
-      </c>
+      <c r="A184" s="6"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
       <c r="D184" s="7"/>
-      <c t="s" r="E184" s="7">
-        <v>268</v>
-      </c>
-      <c r="F184" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G184" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H184" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I184" s="7">
-        <v>269</v>
-      </c>
-      <c t="s" r="J184" s="7">
-        <v>184</v>
-      </c>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="8"/>
+      <c r="H184" s="8"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="7"/>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
@@ -7138,14 +7142,14 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7154,13 +7158,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>270</v>
+        <v>137</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>271</v>
+        <v>129</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7171,29 +7175,29 @@
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>253</v>
+        <v>131</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>103</v>
+        <v>270</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>272</v>
+        <v>185</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7204,14 +7208,14 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7220,13 +7224,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>37</v>
+        <v>272</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7237,45 +7241,63 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c r="M188" s="7"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="6"/>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
+      <c t="s" r="A189" s="6">
+        <v>13</v>
+      </c>
+      <c r="B189" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="C189" s="7">
+        <v>14</v>
+      </c>
       <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="8"/>
-      <c r="H189" s="8"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="7"/>
+      <c t="s" r="E189" s="7">
+        <v>269</v>
+      </c>
+      <c r="F189" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G189" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H189" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I189" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="J189" s="7">
+        <v>37</v>
+      </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
@@ -7285,63 +7307,45 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>621</v>
+        <v>163</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c t="s" r="A191" s="6">
-        <v>13</v>
-      </c>
-      <c r="B191" s="7">
-        <v>632</v>
-      </c>
-      <c t="s" r="C191" s="7">
-        <v>14</v>
-      </c>
+      <c r="A191" s="6"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
       <c r="D191" s="7"/>
-      <c t="s" r="E191" s="7">
-        <v>274</v>
-      </c>
-      <c r="F191" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G191" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H191" s="8">
-        <v>95</v>
-      </c>
-      <c t="s" r="I191" s="7">
-        <v>137</v>
-      </c>
-      <c t="s" r="J191" s="7">
-        <v>88</v>
-      </c>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="7"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
@@ -7351,14 +7355,14 @@
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>729</v>
+        <v>621</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7367,13 +7371,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>251</v>
+        <v>71</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>223</v>
+        <v>128</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7384,29 +7388,29 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>728</v>
+        <v>632</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>95</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>244</v>
+        <v>137</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>231</v>
+        <v>88</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7417,14 +7421,14 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>508</v>
+        <v>729</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7433,13 +7437,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>159</v>
+        <v>225</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7450,45 +7454,63 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>773</v>
+        <v>728</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c r="A196" s="6"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
+      <c t="s" r="A196" s="6">
+        <v>13</v>
+      </c>
+      <c r="B196" s="7">
+        <v>508</v>
+      </c>
+      <c t="s" r="C196" s="7">
+        <v>14</v>
+      </c>
       <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
-      <c r="G196" s="8"/>
-      <c r="H196" s="8"/>
-      <c r="I196" s="7"/>
-      <c r="J196" s="7"/>
+      <c t="s" r="E196" s="7">
+        <v>275</v>
+      </c>
+      <c r="F196" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G196" s="8">
+        <v>95</v>
+      </c>
+      <c t="s" r="H196" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I196" s="7">
+        <v>76</v>
+      </c>
+      <c t="s" r="J196" s="7">
+        <v>159</v>
+      </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
@@ -7498,63 +7520,45 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>719</v>
+        <v>773</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
+        <v>275</v>
+      </c>
+      <c r="F197" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G197" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H197" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I197" s="7">
+        <v>199</v>
+      </c>
+      <c t="s" r="J197" s="7">
         <v>276</v>
-      </c>
-      <c r="F197" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G197" s="8">
-        <v>95</v>
-      </c>
-      <c t="s" r="H197" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="I197" s="7">
-        <v>50</v>
-      </c>
-      <c t="s" r="J197" s="7">
-        <v>192</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c t="s" r="A198" s="6">
-        <v>13</v>
-      </c>
-      <c r="B198" s="7">
-        <v>718</v>
-      </c>
-      <c t="s" r="C198" s="7">
-        <v>14</v>
-      </c>
+      <c r="A198" s="6"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="7"/>
       <c r="D198" s="7"/>
-      <c t="s" r="E198" s="7">
-        <v>276</v>
-      </c>
-      <c r="F198" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G198" s="8">
-        <v>53</v>
-      </c>
-      <c t="s" r="H198" s="8">
-        <v>95</v>
-      </c>
-      <c t="s" r="I198" s="7">
-        <v>112</v>
-      </c>
-      <c t="s" r="J198" s="7">
-        <v>90</v>
-      </c>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
+      <c r="G198" s="8"/>
+      <c r="H198" s="8"/>
+      <c r="I198" s="7"/>
+      <c r="J198" s="7"/>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
@@ -7571,7 +7575,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7580,13 +7584,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7604,19 +7608,19 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>95</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>170</v>
@@ -7637,7 +7641,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7646,13 +7650,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7670,13 +7674,13 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>95</v>
@@ -7685,7 +7689,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7718,7 +7722,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7733,7 +7737,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7751,7 +7755,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7763,10 +7767,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7784,7 +7788,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7796,7 +7800,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>209</v>
@@ -7817,7 +7821,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7832,7 +7836,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7850,7 +7854,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7862,10 +7866,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7883,7 +7887,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7895,10 +7899,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7931,7 +7935,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7940,13 +7944,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7964,19 +7968,19 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>138</v>
@@ -7997,7 +8001,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8006,13 +8010,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8030,22 +8034,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8063,7 +8067,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8072,13 +8076,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8096,13 +8100,13 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>30</v>
@@ -8111,7 +8115,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8144,7 +8148,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8156,7 +8160,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>19</v>
@@ -8192,7 +8196,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8201,10 +8205,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>87</v>
@@ -8225,22 +8229,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8258,19 +8262,19 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>121</v>
@@ -8291,22 +8295,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8324,7 +8328,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8333,13 +8337,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8357,22 +8361,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8405,7 +8409,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8420,7 +8424,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8438,7 +8442,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8453,7 +8457,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8471,7 +8475,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8480,7 +8484,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>93</v>
@@ -8504,19 +8508,19 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>98</v>
@@ -8552,7 +8556,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8564,10 +8568,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8585,7 +8589,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8600,7 +8604,7 @@
         <v>214</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8618,7 +8622,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8627,13 +8631,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8651,19 +8655,19 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>76</v>
@@ -8684,7 +8688,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8693,13 +8697,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8717,13 +8721,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>41</v>
@@ -8732,7 +8736,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8750,7 +8754,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8759,13 +8763,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8783,22 +8787,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8831,7 +8835,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8843,7 +8847,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>165</v>
@@ -8864,7 +8868,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8897,7 +8901,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8909,7 +8913,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>103</v>
@@ -8930,7 +8934,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8939,13 +8943,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8963,13 +8967,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>41</v>
@@ -9011,19 +9015,19 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>109</v>
@@ -9044,7 +9048,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9056,7 +9060,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>113</v>
@@ -9077,7 +9081,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9092,7 +9096,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9110,7 +9114,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9122,10 +9126,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9143,7 +9147,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9191,7 +9195,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9200,13 +9204,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>137</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9224,13 +9228,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>41</v>
@@ -9239,7 +9243,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9257,7 +9261,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9266,7 +9270,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>131</v>
@@ -9290,19 +9294,19 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>84</v>
@@ -9338,7 +9342,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9350,7 +9354,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>140</v>
@@ -9371,7 +9375,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9380,7 +9384,7 @@
         <v>147</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>32</v>
@@ -9404,19 +9408,19 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>147</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>210</v>
@@ -9437,7 +9441,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9452,7 +9456,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9470,7 +9474,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9479,13 +9483,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9503,22 +9507,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9551,7 +9555,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9560,7 +9564,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>128</v>
@@ -9584,13 +9588,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>30</v>
@@ -9599,7 +9603,7 @@
         <v>198</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9617,7 +9621,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9650,7 +9654,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9662,10 +9666,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9683,7 +9687,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9716,7 +9720,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9731,7 +9735,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9764,7 +9768,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9776,7 +9780,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>128</v>
@@ -9797,7 +9801,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9830,7 +9834,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9863,7 +9867,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9878,7 +9882,7 @@
         <v>215</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9896,7 +9900,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9908,10 +9912,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9929,7 +9933,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9938,13 +9942,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9962,13 +9966,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>41</v>
@@ -9977,7 +9981,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10010,7 +10014,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10019,10 +10023,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>113</v>
@@ -10043,13 +10047,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>30</v>
@@ -10076,7 +10080,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10088,7 +10092,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>96</v>
@@ -10124,7 +10128,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10157,7 +10161,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10166,13 +10170,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10190,22 +10194,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10223,7 +10227,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10235,7 +10239,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>326</v>
+        <v>217</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>130</v>
@@ -10256,7 +10260,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10265,10 +10269,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>36</v>
@@ -10289,13 +10293,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>30</v>
@@ -10322,7 +10326,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10355,7 +10359,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10367,7 +10371,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>328</v>
@@ -10418,7 +10422,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10451,7 +10455,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10514,7 +10518,7 @@
         <v>172</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>125</v>
@@ -10547,10 +10551,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10583,7 +10587,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10631,7 +10635,7 @@
         <v>333</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10661,10 +10665,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10727,7 +10731,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>113</v>
@@ -10793,10 +10797,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10859,7 +10863,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>334</v>
@@ -10907,10 +10911,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10937,10 +10941,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>115</v>
@@ -10967,16 +10971,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11006,10 +11010,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11039,10 +11043,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11123,7 +11127,7 @@
         <v>338</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11153,7 +11157,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>122</v>
@@ -11222,7 +11226,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11336,7 +11340,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11363,13 +11367,13 @@
         <v>95</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11393,7 +11397,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>95</v>
@@ -11402,7 +11406,7 @@
         <v>343</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11429,7 +11433,7 @@
         <v>95</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>344</v>
@@ -11459,7 +11463,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>95</v>
@@ -11513,10 +11517,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11546,10 +11550,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11582,7 +11586,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>326</v>
+        <v>217</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11615,7 +11619,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11681,7 +11685,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11723,7 +11727,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>155</v>
@@ -11753,7 +11757,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>30</v>
@@ -11762,7 +11766,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11789,13 +11793,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11819,13 +11823,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>171</v>
@@ -11894,7 +11898,7 @@
         <v>350</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12005,7 +12009,7 @@
         <v>354</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>200</v>
@@ -12083,7 +12087,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>155</v>
@@ -12113,7 +12117,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>41</v>
@@ -12149,10 +12153,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>167</v>
@@ -12179,7 +12183,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>41</v>
@@ -12215,13 +12219,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12245,7 +12249,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>41</v>
@@ -12299,10 +12303,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12332,10 +12336,10 @@
         <v>359</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12443,10 +12447,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>338</v>
@@ -12473,16 +12477,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12515,7 +12519,7 @@
         <v>362</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12548,7 +12552,7 @@
         <v>363</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12626,7 +12630,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>356</v>
@@ -12725,7 +12729,7 @@
         <v>332</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>123</v>
@@ -12758,10 +12762,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12875,7 +12879,7 @@
         <v>367</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12914,7 +12918,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>30</v>
@@ -12950,13 +12954,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12980,16 +12984,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13067,10 +13071,10 @@
         <v>169</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13130,10 +13134,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>113</v>
@@ -13160,16 +13164,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13199,10 +13203,10 @@
         <v>169</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13310,7 +13314,7 @@
         <v>157</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>89</v>
@@ -13340,13 +13344,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>157</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>32</v>
@@ -13415,7 +13419,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13661,7 +13665,7 @@
         <v>363</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13706,10 +13710,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>326</v>
+        <v>217</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13748,16 +13752,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13784,13 +13788,13 @@
         <v>91</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13814,7 +13818,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>91</v>
@@ -13823,7 +13827,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13850,7 +13854,7 @@
         <v>91</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>168</v>
@@ -13880,13 +13884,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>201</v>
@@ -13916,13 +13920,13 @@
         <v>91</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>380</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14003,7 +14007,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>326</v>
+        <v>217</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14117,7 +14121,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14150,7 +14154,7 @@
         <v>384</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14180,10 +14184,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14282,7 +14286,7 @@
         <v>385</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14324,7 +14328,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="I423" s="7">
         <v>128</v>
@@ -14358,13 +14362,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>27</v>
@@ -14397,10 +14401,10 @@
         <v>172</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14433,7 +14437,7 @@
         <v>388</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14463,7 +14467,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>124</v>
@@ -14496,10 +14500,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14526,10 +14530,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>79</v>
@@ -14556,7 +14560,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>41</v>
@@ -14679,7 +14683,7 @@
         <v>391</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14712,7 +14716,7 @@
         <v>392</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14745,7 +14749,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14778,7 +14782,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14805,10 +14809,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>171</v>
@@ -14835,13 +14839,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>389</v>
@@ -14886,7 +14890,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I441" s="7">
         <v>153</v>
@@ -14940,7 +14944,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15033,13 +15037,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>126</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15084,7 +15088,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>156</v>
@@ -15117,10 +15121,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15150,7 +15154,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>132</v>
@@ -15216,7 +15220,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>397</v>
@@ -15330,10 +15334,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15363,10 +15367,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15396,10 +15400,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15477,10 +15481,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15558,7 +15562,7 @@
         <v>95</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>107</v>
@@ -15606,7 +15610,7 @@
         <v>404</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>69</v>
@@ -15642,7 +15646,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -15690,7 +15694,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15723,7 +15727,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15768,10 +15772,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15837,7 +15841,7 @@
         <v>389</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -15915,7 +15919,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>411</v>
@@ -15963,10 +15967,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16113,7 +16117,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16146,7 +16150,7 @@
         <v>417</v>
       </c>
       <c t="s" r="J485" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
